--- a/data/shop.xlsx
+++ b/data/shop.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -82,10 +82,19 @@
     <t>weapon</t>
   </si>
   <si>
-    <t>手枪</t>
-  </si>
-  <si>
-    <t>步枪</t>
+    <t>小木杖</t>
+  </si>
+  <si>
+    <t>学徒法杖</t>
+  </si>
+  <si>
+    <t>法师杖</t>
+  </si>
+  <si>
+    <t>魔杖</t>
+  </si>
+  <si>
+    <t>奥数魔杖</t>
   </si>
 </sst>
 </file>
@@ -1230,8 +1239,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="19.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="40.5555555555556" customWidth="1"/>
@@ -1357,6 +1366,66 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>2000</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>5000</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
